--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484245_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484245_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8447</v>
+        <v>7.4869</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7744</v>
+        <v>6.1988</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0703</v>
+        <v>1.2882</v>
       </c>
       <c r="G2" t="n">
         <v>5.0583</v>
@@ -610,13 +610,13 @@
         <v>2.7348</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3957</v>
+        <v>1.038</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1377</v>
+        <v>0.5621</v>
       </c>
       <c r="U2" t="n">
-        <v>0.258</v>
+        <v>0.4758</v>
       </c>
       <c r="V2" t="n">
         <v>0.6093</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.49</v>
+        <v>3.9424</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7239</v>
+        <v>5.3319</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7661</v>
+        <v>-1.3895</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6832</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5626</v>
+        <v>-1.1627</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1206</v>
+        <v>1.0792</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1311</v>
+        <v>2.7832</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0097</v>
+        <v>0.3543</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1214</v>
+        <v>2.4289</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.448</v>
+        <v>-2.8668</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4472</v>
+        <v>-1.517</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0008</v>
+        <v>-1.3498</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.9069</v>
+        <v>-1.9534</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7881</v>
+        <v>1.2567</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3321</v>
+        <v>0.569</v>
       </c>
       <c r="U3" t="n">
-        <v>0.456</v>
+        <v>0.6877</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1675</v>
+        <v>2.7693</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1675</v>
+        <v>3.9331</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.1638</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1353</v>
+        <v>1.4993</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3614</v>
+        <v>0.9238</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2261</v>
+        <v>0.5755</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.08359999999999999</v>
+        <v>1.6832</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1627</v>
+        <v>1.5626</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0792</v>
+        <v>0.1206</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7832</v>
+        <v>3.1311</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3543</v>
+        <v>3.0097</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4289</v>
+        <v>0.1214</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.8668</v>
+        <v>-1.448</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.517</v>
+        <v>-1.4472</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3498</v>
+        <v>-0.0008</v>
       </c>
       <c r="P4" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.7973</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.532</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.2654</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1675</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1675</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-1.9534</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.9534</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.4495</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.4015</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.8511</v>
-      </c>
-      <c r="V4" t="n">
-        <v>2.7693</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.9331</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-1.1638</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8522</v>
+        <v>1.4844</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8233</v>
+        <v>0.0159</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9711</v>
+        <v>1.4686</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8431999999999999</v>
+        <v>2.8601</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8554</v>
+        <v>0.945</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0122</v>
+        <v>1.9151</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3003</v>
+        <v>3.7589</v>
       </c>
       <c r="K5" t="n">
-        <v>3.0979</v>
+        <v>1.8432</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2023</v>
+        <v>1.9157</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4571</v>
+        <v>-0.8988</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2425</v>
+        <v>-0.8982</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2146</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7814</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>-4.8836</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7348</v>
+        <v>2.5395</v>
       </c>
       <c r="S5" t="n">
-        <v>3.9421</v>
+        <v>1.5229</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4764</v>
+        <v>1.1405</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4657</v>
+        <v>0.3823</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.7145</v>
+        <v>-0.5545</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.7145</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0643</v>
+        <v>1.4792</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1864</v>
+        <v>2.9132</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2507</v>
+        <v>-1.4341</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8601</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.945</v>
+        <v>1.8554</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9151</v>
+        <v>-1.0122</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7589</v>
+        <v>3.3003</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8432</v>
+        <v>3.0979</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9157</v>
+        <v>0.2023</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8988</v>
+        <v>-2.4571</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8982</v>
+        <v>-1.2425</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-1.2146</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.3441</v>
+        <v>0.7814</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.8836</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5395</v>
+        <v>2.7348</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1028</v>
+        <v>2.5691</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9383</v>
+        <v>1.5664</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1645</v>
+        <v>1.0027</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5545</v>
+        <v>-2.7145</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5545</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9745</v>
+        <v>-0.8789</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2332</v>
+        <v>-0.2738</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.6052</v>
       </c>
       <c r="G7" t="n">
         <v>-1.377</v>
@@ -1000,13 +1000,13 @@
         <v>2.1488</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6714</v>
+        <v>0.767</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6219</v>
+        <v>0.5813</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0495</v>
+        <v>0.1856</v>
       </c>
       <c r="V7" t="n">
         <v>-1.441</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9369</v>
+        <v>-1.618</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6399</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2971</v>
+        <v>-1.0792</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4399</v>
@@ -1078,13 +1078,13 @@
         <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1123</v>
+        <v>0.4313</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3715</v>
+        <v>0.4726</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2592</v>
+        <v>-0.0413</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3149</v>
+        <v>-1.8111</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0371</v>
+        <v>-2.3699</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7222</v>
+        <v>0.5587</v>
       </c>
       <c r="G9" t="n">
         <v>-3.36</v>
@@ -1156,13 +1156,13 @@
         <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3456</v>
+        <v>0.1582</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6657</v>
+        <v>0.0015</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3201</v>
+        <v>0.1567</v>
       </c>
       <c r="V9" t="n">
         <v>0.6093</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7757</v>
+        <v>-2.3574</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2789</v>
+        <v>-0.9151</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4968</v>
+        <v>-1.4423</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3532</v>
@@ -1234,13 +1234,13 @@
         <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5359</v>
+        <v>-0.1176</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3631</v>
+        <v>0.0007</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1728</v>
+        <v>-0.1183</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4959</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4783</v>
+        <v>-2.7155</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8374</v>
+        <v>-0.2108</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6409</v>
+        <v>-2.5047</v>
       </c>
       <c r="G11" t="n">
         <v>-6.4779</v>
@@ -1312,13 +1312,13 @@
         <v>2.9301</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1597</v>
+        <v>0.9225</v>
       </c>
       <c r="T11" t="n">
-        <v>0.212</v>
+        <v>0.8387</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0524</v>
+        <v>0.0838</v>
       </c>
       <c r="V11" t="n">
         <v>0.8865</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.906199999999999</v>
+        <v>6.511299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>10.4701</v>
+        <v>11.0752</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.5641</v>
+        <v>-4.564</v>
       </c>
       <c r="G12" t="n">
         <v>-3.6468</v>
@@ -1360,7 +1360,7 @@
         <v>-4.9951</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3483</v>
+        <v>1.348299999999999</v>
       </c>
       <c r="J12" t="n">
         <v>14.1313</v>
@@ -1381,7 +1381,7 @@
         <v>-7.424</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9767999999999999</v>
+        <v>0.9767999999999994</v>
       </c>
       <c r="Q12" t="n">
         <v>-17.5808</v>
@@ -1390,13 +1390,13 @@
         <v>18.5576</v>
       </c>
       <c r="S12" t="n">
-        <v>9.740100000000002</v>
+        <v>10.3454</v>
       </c>
       <c r="T12" t="n">
-        <v>6.6596</v>
+        <v>7.2648</v>
       </c>
       <c r="U12" t="n">
-        <v>3.0805</v>
+        <v>3.0804</v>
       </c>
       <c r="V12" t="n">
         <v>-1.164000000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>G. PRAT PRUNA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7063</v>
+        <v>4.38</v>
       </c>
       <c r="E13" t="n">
-        <v>5.2395</v>
+        <v>5.0354</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5332</v>
+        <v>-0.6554</v>
       </c>
       <c r="G13" t="n">
-        <v>2.0196</v>
+        <v>2.6192</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8872</v>
+        <v>2.8614</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1324</v>
+        <v>-0.2422</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1006</v>
+        <v>3.4775</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3722</v>
+        <v>3.584</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7284</v>
+        <v>-0.1066</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9191</v>
+        <v>-0.8583</v>
       </c>
       <c r="N13" t="n">
-        <v>0.515</v>
+        <v>-0.7226</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4041</v>
+        <v>-0.1356</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5627</v>
+        <v>2.7348</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7581</v>
+        <v>2.9301</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2336</v>
+        <v>-2.1378</v>
       </c>
       <c r="T13" t="n">
-        <v>1.175</v>
+        <v>-0.9064</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0586</v>
+        <v>-1.2314</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1097</v>
+        <v>1.1638</v>
       </c>
       <c r="W13" t="n">
-        <v>3.1593</v>
+        <v>2.6596</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.269</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. PRAT PRUNA</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5023</v>
+        <v>3.6315</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4287</v>
+        <v>4.3294</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9264</v>
+        <v>-0.6979</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6192</v>
+        <v>2.0196</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8614</v>
+        <v>0.8872</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2422</v>
+        <v>1.1324</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4775</v>
+        <v>1.1006</v>
       </c>
       <c r="K14" t="n">
-        <v>3.584</v>
+        <v>0.3722</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1066</v>
+        <v>0.7284</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8583</v>
+        <v>0.9191</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7226</v>
+        <v>0.515</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1356</v>
+        <v>0.4041</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7348</v>
+        <v>1.5627</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9301</v>
+        <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.0155</v>
+        <v>0.1588</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5131</v>
+        <v>0.2649</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5024</v>
+        <v>-0.1061</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1638</v>
+        <v>-0.1097</v>
       </c>
       <c r="W14" t="n">
-        <v>2.6596</v>
+        <v>3.1593</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4959</v>
+        <v>-3.269</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7075</v>
+        <v>2.4859</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9166</v>
+        <v>4.6132</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.2091</v>
+        <v>-2.1273</v>
       </c>
       <c r="G15" t="n">
         <v>3.6374</v>
@@ -1624,13 +1624,13 @@
         <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2386</v>
+        <v>-1.4603</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4758</v>
+        <v>-0.7792</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7628</v>
+        <v>-0.6811</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2772</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.948</v>
+        <v>0.9817</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2485</v>
+        <v>0.1474</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6994</v>
+        <v>0.8343</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2103</v>
@@ -1702,13 +1702,13 @@
         <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5998</v>
+        <v>-0.5661</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0522</v>
+        <v>-0.1533</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5476</v>
+        <v>-0.4128</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.829</v>
+        <v>-0.5179</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8522</v>
+        <v>2.0544</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.6812</v>
+        <v>-2.5723</v>
       </c>
       <c r="G17" t="n">
         <v>0.3976</v>
@@ -1780,13 +1780,13 @@
         <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3085</v>
+        <v>-0.9974</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3631</v>
+        <v>-0.1609</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9454</v>
+        <v>-0.8365</v>
       </c>
       <c r="V17" t="n">
         <v>0.2772</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3363</v>
+        <v>-0.8436</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7119</v>
+        <v>-2.0117</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6245000000000001</v>
+        <v>1.1681</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7806</v>
+        <v>2.9182</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5493</v>
+        <v>1.448</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7687</v>
+        <v>1.4702</v>
       </c>
       <c r="J18" t="n">
-        <v>1.679</v>
+        <v>3.1578</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3126</v>
+        <v>1.1474</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6336000000000001</v>
+        <v>2.0105</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8984</v>
+        <v>-0.2396</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7634</v>
+        <v>0.3006</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.135</v>
+        <v>-0.5403</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7814</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1488</v>
+        <v>-4.8836</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1132</v>
+        <v>-1.2224</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2421</v>
+        <v>-0.5632</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8711</v>
+        <v>-0.6592</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2224</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2224</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4697</v>
+        <v>-0.8903</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7195</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2498</v>
+        <v>-0.3807</v>
       </c>
       <c r="G19" t="n">
-        <v>2.9182</v>
+        <v>0.7806</v>
       </c>
       <c r="H19" t="n">
-        <v>1.448</v>
+        <v>1.5493</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4702</v>
+        <v>-0.7687</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1578</v>
+        <v>1.679</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1474</v>
+        <v>2.3126</v>
       </c>
       <c r="L19" t="n">
-        <v>2.0105</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2396</v>
+        <v>-0.8984</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3006</v>
+        <v>-0.7634</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5403</v>
+        <v>-0.135</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.5395</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.8836</v>
+        <v>-2.1488</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3441</v>
+        <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.8485</v>
+        <v>-0.6672</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.271</v>
+        <v>-0.0399</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5775</v>
+        <v>-0.6274</v>
       </c>
       <c r="V19" t="n">
+        <v>-0.2224</v>
+      </c>
+      <c r="W19" t="n">
         <v>0</v>
       </c>
-      <c r="W19" t="n">
-        <v>0.2772</v>
-      </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>-0.2224</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6656</v>
+        <v>-1.4763</v>
       </c>
       <c r="E20" t="n">
         <v>-1.7855</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1199</v>
+        <v>0.3091</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6975</v>
@@ -2014,13 +2014,13 @@
         <v>2.1488</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8194</v>
+        <v>-0.6301</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1732</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6461</v>
+        <v>-0.4568</v>
       </c>
       <c r="V20" t="n">
         <v>1.8279</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6423</v>
+        <v>-3.7124</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6426</v>
+        <v>-2.4404</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9997</v>
+        <v>-1.272</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7509</v>
@@ -2092,13 +2092,13 @@
         <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1402</v>
+        <v>0.0701</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2421</v>
+        <v>-0.0399</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3823</v>
+        <v>0.11</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6642</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6887</v>
+        <v>-4.3693</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3913</v>
+        <v>-3.0991</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2974</v>
+        <v>-1.2702</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2146</v>
@@ -2170,13 +2170,13 @@
         <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2982</v>
+        <v>-0.9788</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5009</v>
+        <v>-0.2069</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7991</v>
+        <v>-0.7719</v>
       </c>
       <c r="V22" t="n">
         <v>0.3869</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1385</v>
+        <v>-4.9012</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8707</v>
+        <v>-1.7696</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.2677</v>
+        <v>-3.1316</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8524</v>
@@ -2248,13 +2248,13 @@
         <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8722</v>
+        <v>-0.6349</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4237</v>
+        <v>-0.3225</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4485</v>
+        <v>-0.3123</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2186</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.905999999999999</v>
+        <v>-5.231900000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>4.563999999999998</v>
+        <v>4.563899999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.4701</v>
+        <v>-9.7959</v>
       </c>
       <c r="G24" t="n">
         <v>3.646900000000001</v>
@@ -2326,13 +2326,13 @@
         <v>17.5808</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.740099999999998</v>
+        <v>-9.066099999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.0804</v>
+        <v>-3.0805</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.6596</v>
+        <v>-5.9855</v>
       </c>
       <c r="V24" t="n">
         <v>1.1637</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484245_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484245_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,31 +653,31 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9424</v>
+        <v>2.4145</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3319</v>
+        <v>3.804</v>
       </c>
       <c r="F3" t="n">
         <v>-1.3895</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-1.6115</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1627</v>
+        <v>-2.0837</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0792</v>
+        <v>0.4722</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7832</v>
+        <v>1.2553</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3543</v>
+        <v>-0.5667</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4289</v>
+        <v>1.8219</v>
       </c>
       <c r="M3" t="n">
         <v>-2.8668</v>
@@ -704,12 +714,17 @@
       </c>
       <c r="X3" t="n">
         <v>-1.1638</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4993</v>
+        <v>1.5279</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9238</v>
+        <v>1.5279</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5755</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6832</v>
+        <v>1.5279</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5626</v>
+        <v>0.921</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1206</v>
+        <v>0.607</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1311</v>
+        <v>1.5279</v>
       </c>
       <c r="K4" t="n">
-        <v>3.0097</v>
+        <v>0.921</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1214</v>
+        <v>0.607</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.448</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4472</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0008</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7973</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.532</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2654</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1675</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1675</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4844</v>
+        <v>1.4993</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0159</v>
+        <v>0.9238</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4686</v>
+        <v>0.5755</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8601</v>
+        <v>1.6832</v>
       </c>
       <c r="H5" t="n">
-        <v>0.945</v>
+        <v>1.5626</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9151</v>
+        <v>0.1206</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7589</v>
+        <v>3.1311</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8432</v>
+        <v>3.0097</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9157</v>
+        <v>0.1214</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8988</v>
+        <v>-1.448</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8982</v>
+        <v>-1.4472</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0008</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.3441</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.8836</v>
+        <v>-3.9069</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5395</v>
+        <v>1.7581</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5229</v>
+        <v>1.7973</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1405</v>
+        <v>1.532</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3823</v>
+        <v>0.2654</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5545</v>
+        <v>0.1675</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.1675</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4792</v>
+        <v>1.4844</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9132</v>
+        <v>0.0159</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4341</v>
+        <v>1.4686</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8431999999999999</v>
+        <v>2.8601</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8554</v>
+        <v>0.945</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0122</v>
+        <v>1.9151</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3003</v>
+        <v>3.7589</v>
       </c>
       <c r="K6" t="n">
-        <v>3.0979</v>
+        <v>1.8432</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2023</v>
+        <v>1.9157</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.4571</v>
+        <v>-0.8988</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2425</v>
+        <v>-0.8982</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2146</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7814</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>-4.8836</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7348</v>
+        <v>2.5395</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5691</v>
+        <v>1.5229</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5664</v>
+        <v>1.1405</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0027</v>
+        <v>0.3823</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.7145</v>
+        <v>-0.5545</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.7145</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8789</v>
+        <v>1.4792</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2738</v>
+        <v>2.9132</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6052</v>
+        <v>-1.4341</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.377</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.756</v>
+        <v>1.8554</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.621</v>
+        <v>-1.0122</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1216</v>
+        <v>3.3003</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2021</v>
+        <v>3.0979</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3237</v>
+        <v>0.2023</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4986</v>
+        <v>-2.4571</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5538</v>
+        <v>-1.2425</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9447</v>
+        <v>-1.2146</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1488</v>
+        <v>2.7348</v>
       </c>
       <c r="S7" t="n">
-        <v>0.767</v>
+        <v>2.5691</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5813</v>
+        <v>1.5664</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1856</v>
+        <v>1.0027</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.441</v>
+        <v>-2.7145</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.441</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.618</v>
+        <v>-0.8789</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.2738</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0792</v>
+        <v>-0.6052</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4399</v>
+        <v>-1.377</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9814</v>
+        <v>-0.756</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4585</v>
+        <v>-0.621</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.0114</v>
+        <v>0.1216</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6322</v>
+        <v>-0.2021</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6208</v>
+        <v>0.3237</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4285</v>
+        <v>-1.4986</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3492</v>
+        <v>-0.5538</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0793</v>
+        <v>-0.9447</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3907</v>
+        <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4313</v>
+        <v>0.767</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4726</v>
+        <v>0.5813</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0413</v>
+        <v>0.1856</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.441</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.441</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8111</v>
+        <v>-1.618</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3699</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5587</v>
+        <v>-1.0792</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.36</v>
+        <v>-2.4399</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9573</v>
+        <v>-1.9814</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4027</v>
+        <v>-0.4585</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6523</v>
+        <v>-1.0114</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0591</v>
+        <v>-1.6322</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.6208</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7077</v>
+        <v>-1.4285</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8982</v>
+        <v>-0.3492</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8095</v>
+        <v>-1.0793</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1582</v>
+        <v>0.4313</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0015</v>
+        <v>0.4726</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1567</v>
+        <v>-0.0413</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.719</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.3283</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. COSTA RABANEDA</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3574</v>
+        <v>-1.8111</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9151</v>
+        <v>-2.3699</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4423</v>
+        <v>0.5587</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3532</v>
+        <v>-3.36</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5285</v>
+        <v>-1.9573</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1753</v>
+        <v>-1.4027</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0609</v>
+        <v>-1.6523</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0205</v>
+        <v>-1.0591</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0405</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4142</v>
+        <v>-1.7077</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.549</v>
+        <v>-0.8982</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1348</v>
+        <v>-0.8095</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1176</v>
+        <v>0.1582</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0007</v>
+        <v>0.0015</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1183</v>
+        <v>0.1567</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4959</v>
+        <v>0.6093</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.719</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4959</v>
+        <v>1.3283</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>M. COSTA RABANEDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7155</v>
+        <v>-2.3574</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2108</v>
+        <v>-0.9151</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5047</v>
+        <v>-1.4423</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.4779</v>
+        <v>-0.3532</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.6596</v>
+        <v>-0.5285</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.8184</v>
+        <v>0.1753</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.3417</v>
+        <v>0.0609</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.1426</v>
+        <v>0.0205</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1992</v>
+        <v>0.0405</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.1362</v>
+        <v>-0.4142</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.517</v>
+        <v>-0.549</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.6192</v>
+        <v>0.1348</v>
       </c>
       <c r="P11" t="n">
-        <v>1.9534</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9301</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9225</v>
+        <v>-0.1176</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8387</v>
+        <v>0.0007</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0838</v>
+        <v>-0.1183</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8865</v>
+        <v>-1.4959</v>
       </c>
       <c r="W11" t="n">
-        <v>3.269</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.3824</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,151 +1400,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.511299999999999</v>
+        <v>-2.7155</v>
       </c>
       <c r="E12" t="n">
-        <v>11.0752</v>
+        <v>-0.2108</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.564</v>
+        <v>-2.5047</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.6468</v>
+        <v>-6.4779</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.9951</v>
+        <v>-3.6596</v>
       </c>
       <c r="I12" t="n">
-        <v>1.348299999999999</v>
+        <v>-2.8184</v>
       </c>
       <c r="J12" t="n">
-        <v>14.1313</v>
+        <v>-3.3417</v>
       </c>
       <c r="K12" t="n">
-        <v>5.3592</v>
+        <v>-2.1426</v>
       </c>
       <c r="L12" t="n">
-        <v>8.7721</v>
+        <v>-1.1992</v>
       </c>
       <c r="M12" t="n">
-        <v>-17.7784</v>
+        <v>-3.1362</v>
       </c>
       <c r="N12" t="n">
-        <v>-10.3543</v>
+        <v>-1.517</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.424</v>
+        <v>-1.6192</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9767999999999994</v>
+        <v>1.9534</v>
       </c>
       <c r="Q12" t="n">
-        <v>-17.5808</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>18.5576</v>
+        <v>2.9301</v>
       </c>
       <c r="S12" t="n">
-        <v>10.3454</v>
+        <v>0.9225</v>
       </c>
       <c r="T12" t="n">
-        <v>7.2648</v>
+        <v>0.8387</v>
       </c>
       <c r="U12" t="n">
-        <v>3.0804</v>
+        <v>0.0838</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.164000000000001</v>
+        <v>0.8865</v>
       </c>
       <c r="W12" t="n">
-        <v>7.2599</v>
+        <v>3.269</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.4238</v>
+        <v>-2.3824</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. PRAT PRUNA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C.B. GRANOLLERS</t>
+          <t>CB NAVÀS VISCOLA</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.38</v>
+        <v>6.5113</v>
       </c>
       <c r="E13" t="n">
-        <v>5.0354</v>
+        <v>11.0752</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6554</v>
+        <v>-4.564</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6192</v>
+        <v>-3.6468</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8614</v>
+        <v>-4.995100000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2422</v>
+        <v>1.3483</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4775</v>
+        <v>14.1313</v>
       </c>
       <c r="K13" t="n">
-        <v>3.584</v>
+        <v>5.359200000000002</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1066</v>
+        <v>8.772100000000002</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8583</v>
+        <v>-17.7784</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7226</v>
+        <v>-10.3543</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1356</v>
+        <v>-7.423999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>2.7348</v>
+        <v>0.9768000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1953</v>
+        <v>-17.5808</v>
       </c>
       <c r="R13" t="n">
-        <v>2.9301</v>
+        <v>18.5576</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1378</v>
+        <v>10.3454</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9064</v>
+        <v>7.2648</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2314</v>
+        <v>3.0804</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1638</v>
+        <v>-1.164000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>2.6596</v>
+        <v>7.2599</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4959</v>
-      </c>
+        <v>-8.4238</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>G. PRAT PRUNA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6315</v>
+        <v>4.38</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3294</v>
+        <v>5.0354</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6979</v>
+        <v>-0.6554</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0196</v>
+        <v>2.6192</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8872</v>
+        <v>2.8614</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1324</v>
+        <v>-0.2422</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1006</v>
+        <v>3.4775</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3722</v>
+        <v>3.584</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7284</v>
+        <v>-0.1066</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9191</v>
+        <v>-0.8583</v>
       </c>
       <c r="N14" t="n">
-        <v>0.515</v>
+        <v>-0.7226</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4041</v>
+        <v>-0.1356</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5627</v>
+        <v>2.7348</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>2.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1588</v>
+        <v>-2.1378</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2649</v>
+        <v>-0.9064</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1061</v>
+        <v>-1.2314</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1097</v>
+        <v>1.1638</v>
       </c>
       <c r="W14" t="n">
-        <v>3.1593</v>
+        <v>2.6596</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.269</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4859</v>
+        <v>3.6315</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6132</v>
+        <v>4.3294</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1273</v>
+        <v>-0.6979</v>
       </c>
       <c r="G15" t="n">
-        <v>3.6374</v>
+        <v>2.0196</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2205</v>
+        <v>0.8872</v>
       </c>
       <c r="I15" t="n">
-        <v>3.8579</v>
+        <v>1.1324</v>
       </c>
       <c r="J15" t="n">
-        <v>6.3691</v>
+        <v>1.1006</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7572</v>
+        <v>0.3722</v>
       </c>
       <c r="L15" t="n">
-        <v>5.6119</v>
+        <v>0.7284</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.7318</v>
+        <v>0.9191</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9777</v>
+        <v>0.515</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.754</v>
+        <v>0.4041</v>
       </c>
       <c r="P15" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4603</v>
+        <v>0.1588</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7792</v>
+        <v>0.2649</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6811</v>
+        <v>-0.1061</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2772</v>
+        <v>-0.1097</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.1593</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
+        <v>-3.269</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9817</v>
+        <v>2.4859</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1474</v>
+        <v>4.6132</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8343</v>
+        <v>-2.1273</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2103</v>
+        <v>3.6374</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1699</v>
+        <v>-0.2205</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0405</v>
+        <v>3.8579</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2188</v>
+        <v>6.3691</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1241</v>
+        <v>0.7572</v>
       </c>
       <c r="L16" t="n">
-        <v>0.09470000000000001</v>
+        <v>5.6119</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4291</v>
+        <v>-2.7318</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2939</v>
+        <v>-0.9777</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1352</v>
+        <v>-1.754</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5661</v>
+        <v>-1.4603</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1533</v>
+        <v>-0.7792</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4128</v>
+        <v>-0.6811</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5179</v>
+        <v>1.221</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0544</v>
+        <v>1.221</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5723</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3976</v>
+        <v>1.221</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0184</v>
+        <v>0.614</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6208</v>
+        <v>0.607</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3055</v>
+        <v>1.221</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5771</v>
+        <v>0.614</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7284</v>
+        <v>0.607</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9079</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5587</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3492</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9974</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1609</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8365</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8436</v>
+        <v>0.607</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0117</v>
+        <v>0.607</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1681</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>2.9182</v>
+        <v>0.607</v>
       </c>
       <c r="H18" t="n">
-        <v>1.448</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4702</v>
+        <v>0.607</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1578</v>
+        <v>0.607</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1474</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2.0105</v>
+        <v>0.607</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2396</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3006</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5403</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.5395</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.8836</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2224</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5632</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6592</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8903</v>
+        <v>0.3747</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.4596</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3807</v>
+        <v>0.8343</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7806</v>
+        <v>-0.8173</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5493</v>
+        <v>-0.1699</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7687</v>
+        <v>-0.6475</v>
       </c>
       <c r="J19" t="n">
-        <v>1.679</v>
+        <v>-0.3882</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3126</v>
+        <v>0.1241</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.5122</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8984</v>
+        <v>-0.4291</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7634</v>
+        <v>-0.2939</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.135</v>
+        <v>-0.1352</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6672</v>
+        <v>-0.5661</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0399</v>
+        <v>-0.1533</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6274</v>
+        <v>-0.4128</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2224</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2224</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4763</v>
+        <v>-0.5179</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7855</v>
+        <v>2.0544</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3091</v>
+        <v>-2.5723</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6975</v>
+        <v>0.3976</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6055</v>
+        <v>1.0184</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.092</v>
+        <v>-0.6208</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3147</v>
+        <v>2.3055</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3722</v>
+        <v>1.5771</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6869</v>
+        <v>0.7284</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3828</v>
+        <v>-1.9079</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9777</v>
+        <v>-0.5587</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4051</v>
+        <v>-1.3492</v>
       </c>
       <c r="P20" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-3.1255</v>
-      </c>
       <c r="R20" t="n">
-        <v>2.1488</v>
+        <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6301</v>
+        <v>-0.9974</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1732</v>
+        <v>-0.1609</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4568</v>
+        <v>-0.8365</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8279</v>
+        <v>0.2772</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8279</v>
+        <v>0.8865</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7124</v>
+        <v>-0.8903</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4404</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.272</v>
+        <v>-0.3807</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7509</v>
+        <v>0.7806</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2673</v>
+        <v>1.5493</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4836</v>
+        <v>-0.7687</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2171</v>
+        <v>1.679</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0819</v>
+        <v>2.3126</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1352</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.968</v>
+        <v>-0.8984</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3492</v>
+        <v>-0.7634</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.6188</v>
+        <v>-0.135</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3674</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>-2.1488</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0701</v>
+        <v>-0.6672</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0399</v>
       </c>
       <c r="U21" t="n">
-        <v>0.11</v>
+        <v>-0.6274</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6642</v>
+        <v>-0.2224</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.2224</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3693</v>
+        <v>-1.4763</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0991</v>
+        <v>-1.7855</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2702</v>
+        <v>0.3091</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2146</v>
+        <v>-1.6975</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.461</v>
+        <v>-0.6055</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7536</v>
+        <v>-1.092</v>
       </c>
       <c r="J22" t="n">
-        <v>0.038</v>
+        <v>-0.3147</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0973</v>
+        <v>0.3722</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1352</v>
+        <v>-0.6869</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.2526</v>
+        <v>-1.3828</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3638</v>
+        <v>-0.9777</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.8889</v>
+        <v>-0.4051</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5627</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>-3.1255</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9788</v>
+        <v>-0.6301</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2069</v>
+        <v>-0.1732</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7719</v>
+        <v>-0.4568</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3869</v>
+        <v>1.8279</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9012</v>
+        <v>-2.0646</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7696</v>
+        <v>-3.2327</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1316</v>
+        <v>1.1681</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8524</v>
+        <v>1.6972</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.045</v>
+        <v>0.834</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8073</v>
+        <v>0.8632</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4704</v>
+        <v>1.9368</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1228</v>
+        <v>0.5334</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5931999999999999</v>
+        <v>1.4035</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.382</v>
+        <v>-0.2396</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1678</v>
+        <v>0.3006</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2142</v>
+        <v>-0.5403</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1953</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9767</v>
+        <v>-4.8836</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7814</v>
+        <v>2.3441</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6349</v>
+        <v>-1.2224</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3225</v>
+        <v>-0.5632</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3123</v>
+        <v>-0.6592</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,318 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.231900000000001</v>
+        <v>-3.7124</v>
       </c>
       <c r="E24" t="n">
-        <v>4.563899999999999</v>
+        <v>-2.4404</v>
       </c>
       <c r="F24" t="n">
+        <v>-1.272</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.7509</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.2673</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.4836</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.2171</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.0819</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.968</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.3492</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.6188</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.0399</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>J. JUAREZ GIMENEZ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-4.3693</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.0991</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.2702</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.2146</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.461</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.7536</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.0973</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-2.2526</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.3638</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-1.8889</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.9788</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.2069</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.7719</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>M. SALMERON SEGU</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-4.9012</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.7696</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-3.1316</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-2.8524</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.045</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.8073</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.4704</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.1228</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.5931999999999999</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-2.382</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.1678</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.2142</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.6349</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.3225</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.3123</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484245_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-5.231900000000003</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4.563899999999997</v>
+      </c>
+      <c r="F27" t="n">
         <v>-9.7959</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G27" t="n">
         <v>3.646900000000001</v>
       </c>
-      <c r="H24" t="n">
-        <v>4.9951</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-1.348200000000001</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="H27" t="n">
+        <v>4.995099999999999</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.3482</v>
+      </c>
+      <c r="J27" t="n">
         <v>17.7783</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K27" t="n">
         <v>10.3542</v>
       </c>
-      <c r="L24" t="n">
-        <v>7.424000000000001</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="L27" t="n">
+        <v>7.424100000000001</v>
+      </c>
+      <c r="M27" t="n">
         <v>-14.1314</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N27" t="n">
         <v>-5.3592</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O27" t="n">
         <v>-8.7722</v>
       </c>
-      <c r="P24" t="n">
-        <v>-0.9767000000000001</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="P27" t="n">
+        <v>-0.9767000000000006</v>
+      </c>
+      <c r="Q27" t="n">
         <v>-18.5574</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R27" t="n">
         <v>17.5808</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S27" t="n">
         <v>-9.066099999999999</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T27" t="n">
         <v>-3.0805</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U27" t="n">
         <v>-5.9855</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V27" t="n">
         <v>1.1637</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W27" t="n">
         <v>8.423500000000001</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X27" t="n">
         <v>-7.2599</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
